--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:12</t>
+    <t xml:space="preserve">2026-10-01 16:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 16:34</t>
+    <t xml:space="preserve">2026-10-01 19:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:20</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_sexo_e_rezmat_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 06:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -685,7 +685,7 @@
         <v>6.6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
